--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-703.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.5%</t>
+          <t>420.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.2%</t>
+          <t>-601.4%</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-281.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-59.7%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-347.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-169.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.4%</t>
+          <t>-305.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-209.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.0%</t>
+          <t>-219.1%</t>
         </is>
       </c>
     </row>
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1773899318021211</v>
+        <v>-0.2061111240075822</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.063522681384964</v>
+        <v>3.05203420450278</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.498653826120122</v>
+        <v>1.469932633914661</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.034027374091633</v>
+        <v>4.016794658768356</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2431573218515332</v>
+        <v>-0.2718785140569943</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.038233334495669</v>
+        <v>3.026744857613485</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.498653826120122</v>
+        <v>1.469932633914661</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.035044983222103</v>
+        <v>4.017812267898827</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.2854139978337039</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>3.011958696090557</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.498653826120122</v>
+        <v>1.469932633914661</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.025673015209859</v>
+        <v>4.008440299886582</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.3671858982614556</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>2.969332661874694</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.525689399526259</v>
+        <v>1.496968207320798</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.031977085208779</v>
+        <v>4.014744369885502</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.4343950061333333</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>2.947214335559645</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.525689399526259</v>
+        <v>1.496968207320798</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.036742402042481</v>
+        <v>4.019509686719204</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.6419607905249451</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.862012817922241</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.318123615134647</v>
+        <v>1.289402422929186</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.910027727526755</v>
+        <v>3.892795012203478</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-1.059714814071782</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.692838100008569</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9003695915878102</v>
+        <v>0.8716483993823488</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.657302204903716</v>
+        <v>3.640069489580439</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.2813367476299</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.604055543184244</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.8341222656949798</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.617420025966939</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.489340805982977</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.525746064396938</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.8341222656949798</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.622312170520865</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.700753226870952</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.436262552379736</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.6227098448070048</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.490546174326068</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-2.039911604459475</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.293683500650777</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.2835514672184827</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.280135447079403</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.367928826186954</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.182814901698553</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>-0.04446575450899648</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.103663403781684</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-2.861253697722132</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>1.993583703493051</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.1494518687486152</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.048770485646481</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.353638725746229</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.797736084327144</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.6418368967727119</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.754445860875756</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.738819116676301</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.642206466767978</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.6418368967727119</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.752988399688619</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-4.082501889902963</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.506502480931929</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.7497429487999301</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.690013891926904</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.440152240141312</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.359548399492848</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.107393299038278</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.471529740440153</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.749386343137362</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.237627684994687</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.107393299038278</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.473302667140413</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.18119213628715</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>1.051238255202177</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.243810795479545</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.377785056743057</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.415886130419702</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>0.9456454325512462</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.23747452825029</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.369871592082701</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.751548777650155</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.8099609653150304</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.23747452825029</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.368452183738666</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-6.115175022550468</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.6709980275891465</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.335696165117416</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.316006761852632</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.480302405189215</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.5242015895394796</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.632006949416428</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.137474806279056</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-6.888891182369893</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.3595276226819673</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.891083083985408</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.301873666510986</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.1895200614969905</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.886268516456869</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.718265540797984</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>0.02095736239106882</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.884262567065746</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-8.094942551327827</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.1194547511521895</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.894521257734425</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.440817373312637</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.2617051148004181</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.89062082288012</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.60295964377573</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.3281571029306547</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-2.040595726597107</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.889025742935121</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-8.899620985585928</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.4430426637255258</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.109338862330985</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.851558837424002</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.332970093696163</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.6204086115040228</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.109338862330985</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.847532532889599</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.715971482438794</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.7737112683226592</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.109338862330985</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.847430431568015</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-9.873370362651915</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.8340993044364775</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.266737742544106</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.755562619411573</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.23290068515592</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-0.9725611301400283</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.266737742544106</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.760912922709623</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.55930071382093</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.095205121648856</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.593137771209119</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.572988925467792</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.77844968189513</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.179822958256766</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.812286739283317</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.444541295245043</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.77475875693872</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.178346588274202</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.812286739283317</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.444541295245043</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-10.97901693226858</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.254536661287505</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.939925683897306</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.373471125595292</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.19705470389976</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.337269215455539</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.114696451993205</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.273091219222188</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-11.12358487223231</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.292509581295139</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-3.041226620325756</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.332544819716079</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.29870928961885</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.348004127502239</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.2163510377123</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.242025390031669</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.53316138363334</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.449004130009631</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.2163510377123</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.234806225130073</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.82096522817058</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.570797858598503</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.504154882249538</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.055451727633754</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-12.05078967533441</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.661611847625477</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.666802419319699</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>0.9589789952302139</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.28281859507067</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.751729686890866</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.728815116508122</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9244651055462749</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.23080308110185</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.726933145616941</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.728815116508122</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9284554412326758</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.37247492282597</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.78507710920533</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.728815116508122</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.9269802143339341</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.47138166328525</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.809586395224169</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.827721856967397</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.8826895802232411</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.27222955604815</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.742976685976012</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.662399331017584</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>0.9688319621464458</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-12.04638440332874</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.643059551852039</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.620472655430421</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.003567040534953</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.76010959100605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.527410482366902</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.620472655430421</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.004706185091012</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.81300487905033</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.545934823422509</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.615517309341974</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.010313166906187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.52909614812158</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.426637626812373</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.615517309341974</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.016046871144824</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.41367522398349</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.390206519551</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.500096385203879</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.075562163233815</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-11.14983835677942</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.294555253982279</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.500096385203879</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.065678681920908</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.88259655591102</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.189493094134294</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.500096385203879</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.063844121421534</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.7592906274328</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.140471037716468</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.410678714076316</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.117194409124611</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.73533708645684</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.130221115180591</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.386725173100358</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.132235039855679</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.47127714813405</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-1.037857456013224</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.122665234777562</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.277410686687605</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.764197524629209</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.7578126402715899</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.122665234777562</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.274623653027304</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.724013226263018</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.7413952970372724</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-3.082480936411371</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.29907785593486</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.643943430725214</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.7100005576013935</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-3.002411140873567</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.346486554478299</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.410462208495616</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.6086836398717024</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.768929918643968</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.494499716653911</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.230753678351743</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.539692438127112</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.711758414481273</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.525910408838569</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-9.098478204720855</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.49141476192773</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.579482940850386</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.600643179764128</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.907878530047702</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.4123598313708321</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.388883266177233</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.717818045255656</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.658878731364121</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.2998535706737409</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.388883266177233</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.730724386479315</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.764468721137225</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.4700654961822011</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.494473255950338</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.539394463016234</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.783203623255822</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.4290151151525539</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.494473255950338</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.58793880489332</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.635263581848223</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.4897180212776817</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.47415234004178</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.480252431750287</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.611034945459251</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.4887405529755706</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.449923703652808</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.486075627330192</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.567486538688559</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.4782818023623872</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.449923703652808</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.479115015235099</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.296616953029238</v>
+        <v>-8.325338145234701</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3554716137175156</v>
+        <v>-0.3669600905997008</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.449923703652808</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.493577369616242</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.233387581260891</v>
+        <v>-8.262108773466354</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3356477445509816</v>
+        <v>-0.3471362214331668</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.449923703652808</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.488109490075437</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.110096446443761</v>
+        <v>-8.138817638649224</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2888331966135529</v>
+        <v>-0.3003216734957381</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.326632568835678</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.559582264976292</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.088947247540318</v>
+        <v>-8.117668439745781</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2726725388148505</v>
+        <v>-0.2841610156970358</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.305483369932234</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.579972762555684</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.845181805556874</v>
+        <v>-7.873902997762337</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1793856536744225</v>
+        <v>-0.1908741305566077</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.305483369932234</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.575753470902734</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.581153738363614</v>
+        <v>-7.609874930569077</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07165011287710232</v>
+        <v>-0.08313858975928756</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.103617971116281</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.716229739435599</v>
+        <v>1.698997024112322</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.33130334441454</v>
+        <v>-7.360024536620003</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02103211968622931</v>
+        <v>0.009543642804044072</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.103617971116281</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.708971814419301</v>
+        <v>1.691739099096024</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.027735855410561</v>
+        <v>-7.056457047616024</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1460582388084699</v>
+        <v>0.1345697619262847</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.103617971116281</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.71257093793995</v>
+        <v>1.695338222616673</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.954255946558547</v>
+        <v>-6.98297713876401</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1887777084038289</v>
+        <v>0.1772892315216437</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.001416870058805</v>
+        <v>-2.030138062264267</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.769986389305712</v>
+        <v>1.752753673982435</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.729222946889724</v>
+        <v>-6.757944139095187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.277811385887655</v>
+        <v>0.2663229090054697</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.776383870389982</v>
+        <v>-1.805105062595444</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.904026666723303</v>
+        <v>1.886793951400026</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.514588569253317</v>
+        <v>-6.54330976145878</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.368359937996535</v>
+        <v>0.3568714611143498</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.590470684959037</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.037502094359464</v>
+        <v>2.020269379036188</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.247988212278965</v>
+        <v>-6.276709404484428</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4561943395700716</v>
+        <v>0.4447058626878864</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.590470684959037</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.01869635314326</v>
+        <v>2.001463637819983</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.007557715474105</v>
+        <v>-6.036278907679568</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5541096149168929</v>
+        <v>0.5426211380347077</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.350040188154177</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.164697727851054</v>
+        <v>2.147465012527777</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.76476690782466</v>
+        <v>-5.793488100030123</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6551552518114914</v>
+        <v>0.6436667749293061</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.350040188154177</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.168627041685874</v>
+        <v>2.151394326362597</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.648827058199474</v>
+        <v>-5.677548250404937</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7022097755789054</v>
+        <v>0.6907212986967202</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.273218457138053</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.215398664212888</v>
+        <v>2.198165948889611</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406171469776311</v>
+        <v>-5.434892661981774</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7962700821681645</v>
+        <v>0.7847816052859793</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.273218457138053</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.212396735432882</v>
+        <v>2.195164020109605</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.1861506717393</v>
+        <v>-5.214871863944763</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8858574383935829</v>
+        <v>0.8743689615113976</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.131998612070072</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.298707679484284</v>
+        <v>2.281474964161007</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.986902041834491</v>
+        <v>-5.015623234039954</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9814510731573298</v>
+        <v>0.9699625962751446</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.131998612070072</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.314601862286107</v>
+        <v>2.29736914696283</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.827386938315121</v>
+        <v>-4.856108130520584</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.04640295900538</v>
+        <v>1.034914482123194</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9437623163452412</v>
+        <v>-0.9724835085507025</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.411456768838031</v>
+        <v>2.394224053514754</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.682714793215384</v>
+        <v>-4.711435985420847</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.114359919606714</v>
+        <v>1.102871442724529</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7990901712455039</v>
+        <v>-0.8278113634509652</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.508348158459313</v>
+        <v>2.491115443136037</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.742589620573076</v>
+        <v>-4.771310812778539</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.076447480065063</v>
+        <v>1.064959003182878</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8876861908086573</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.458460753446124</v>
+        <v>2.441228038122847</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.655790122794068</v>
+        <v>-4.684511314999531</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.133567772499233</v>
+        <v>1.122079295617048</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8876861908086573</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.48086124676869</v>
+        <v>2.463628531445413</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.556097508065056</v>
+        <v>-4.584818700270519</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.17351721976425</v>
+        <v>1.162028742882064</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7592723838741842</v>
+        <v>-0.7879935760796455</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.540749216979509</v>
+        <v>2.523516501656232</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473593</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.624467694389066</v>
+        <v>-4.653188886594529</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.157176067709348</v>
+        <v>1.145687590827162</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7787178770434305</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.55732155887594</v>
+        <v>2.540088843552663</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978362</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.50305126476259</v>
+        <v>-4.531772456968053</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196179348191829</v>
+        <v>1.184690871309644</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7787178770434305</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.547758267507831</v>
+        <v>2.530525552184554</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.534044424091295</v>
+        <v>-4.562765616296758</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.008491649500734</v>
+        <v>0.9970031726185489</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7787178770434305</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.372467832548218</v>
+        <v>2.355235117224941</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.358570164298825</v>
+        <v>-4.387291356504289</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.08324858540951</v>
+        <v>1.071760108527325</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7787178770434305</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.377035064540006</v>
+        <v>2.359802349216729</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.469506416940074</v>
+        <v>-4.498227609145538</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.038885558239808</v>
+        <v>1.027397081357623</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7787178770434305</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.377046538426804</v>
+        <v>2.359813823103527</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.672532994483308</v>
+        <v>-4.701254186688771</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.96080631244242</v>
+        <v>0.9493178355602347</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9817444545866639</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.258361977120769</v>
+        <v>2.241129261797492</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734154</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.514607395548015</v>
+        <v>-4.543328587753478</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.03414893844867</v>
+        <v>1.022660461566484</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9817444545866639</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.268534363552901</v>
+        <v>2.251301648229624</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212291</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.662928649359143</v>
+        <v>-4.691649841564606</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9697667074980785</v>
+        <v>0.9582782306158932</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9817444545866639</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.263480634126762</v>
+        <v>2.246247918803485</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786038</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.664111734010204</v>
+        <v>-4.692832926215667</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9610692490821797</v>
+        <v>0.9495807721999945</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.9873875030531755</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.251870580491381</v>
+        <v>2.234637865168104</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273184</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.540984027016121</v>
+        <v>-4.569705219221584</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.010872204912915</v>
+        <v>0.9993837280307294</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.9873875030531755</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.252422453524482</v>
+        <v>2.235189738201205</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279493</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.448173545565261</v>
+        <v>-4.476894737770724</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9772690893846241</v>
+        <v>0.9657806125024389</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8658558293968548</v>
+        <v>-0.8945770216023161</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.237381434286363</v>
+        <v>2.220148718963086</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.467973119569465</v>
+        <v>3.746742974678689</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.396756726552849</v>
+        <v>-4.398084748685088</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9997092929141898</v>
+        <v>0.999178084061294</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8144390103844423</v>
+        <v>-0.8157670325166799</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.270105001618412</v>
+        <v>2.269308188339069</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.4%</t>
+          <t>-604.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-63.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.3%</t>
+          <t>-277.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.6%</t>
+          <t>-308.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.1%</t>
+          <t>-220.9%</t>
         </is>
       </c>
     </row>
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.398084748685088</v>
+        <v>-4.428331685549694</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.999178084061294</v>
+        <v>0.9870793093154515</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8157670325166799</v>
+        <v>-0.8460139693812859</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.269308188339069</v>
+        <v>2.251160026220306</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-41.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-220.9%</t>
+          <t>-176.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1947"/>
+  <dimension ref="A1:G1948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.746742974678689</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46342,6 +46342,29 @@
       </c>
       <c r="G1947" t="n">
         <v>2.251160026220306</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="2" t="n">
+        <v>45410</v>
+      </c>
+      <c r="B1948" t="n">
+        <v>3.746765565882249</v>
+      </c>
+      <c r="C1948" t="n">
+        <v>2.701818870948271</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>-4.428331685549694</v>
+      </c>
+      <c r="E1948" t="n">
+        <v>0.9870793093154515</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>-0.8460139693812859</v>
+      </c>
+      <c r="G1948" t="n">
+        <v>2.694882667934639</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-35.3%</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.4%</t>
+          <t>420.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>-64.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.5%</t>
+          <t>-272.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.5%</t>
+          <t>-170.4%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262048</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>3.047708851382481</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.684511314999531</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.122079295617048</v>
+        <v>1.173547901068922</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.8876861908086573</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.463628531445413</v>
+        <v>2.515097136897287</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.047781252755894</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.584818700270519</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.162028742882064</v>
+        <v>1.213497348333939</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.7879935760796455</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.523516501656232</v>
+        <v>2.574985107108107</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.058788175230596</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.653188886594529</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.145687590827162</v>
+        <v>1.197156196279037</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.7787178770434305</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.540088843552663</v>
+        <v>2.591557449004537</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.049224883862487</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.531772456968053</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.184690871309644</v>
+        <v>1.236159476761518</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.7787178770434305</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.530525552184554</v>
+        <v>2.581994157636429</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.873934448902874</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.562765616296758</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9970031726185489</v>
+        <v>1.048471778070423</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.7787178770434305</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.355235117224941</v>
+        <v>2.406703722676816</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.878501680894662</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.387291356504289</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.071760108527325</v>
+        <v>1.123228713979199</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.7787178770434305</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.359802349216729</v>
+        <v>2.411270954668603</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>2.878513154781459</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.498227609145538</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.027397081357623</v>
+        <v>1.078865686809497</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.7787178770434305</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.359813823103527</v>
+        <v>2.411282428555401</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>2.881644540001365</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.701254186688771</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9493178355602347</v>
+        <v>1.000786441012109</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.9817444545866639</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.241129261797492</v>
+        <v>2.292597867249366</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>2.891816926433497</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.543328587753478</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.022660461566484</v>
+        <v>1.074129067018359</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.9817444545866639</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.251301648229624</v>
+        <v>2.302770253681499</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>2.886763197007357</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.691649841564606</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9582782306158932</v>
+        <v>1.009746836067767</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.9817444545866639</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.246247918803485</v>
+        <v>2.297716524255359</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>2.878538972451883</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.692832926215667</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9495807721999945</v>
+        <v>1.001049377651869</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.9873875030531755</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.234637865168104</v>
+        <v>2.286106470619978</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>2.879090845484984</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.569705219221584</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9993837280307294</v>
+        <v>1.050852333482604</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.9873875030531755</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.235189738201205</v>
+        <v>2.286658343653079</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.80836353737635</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.476894737770724</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9657806125024389</v>
+        <v>1.017249217954313</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8945770216023161</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.220148718963086</v>
+        <v>2.271617324414961</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.810237013300951</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.428331685549694</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9870793093154515</v>
+        <v>1.038547914767326</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.8460139693812859</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.251160026220306</v>
+        <v>2.30262863167218</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.746765565882249</v>
+        <v>3.742979813506719</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.701818870948271</v>
+        <v>2.763588057015547</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.428331685549694</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9870793093154515</v>
+        <v>1.038547914767326</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.8460139693812859</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.694882667934639</v>
+        <v>2.756651854001915</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.3%</t>
+          <t>-45.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-703.2%</t>
+          <t>-700.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.3%</t>
+          <t>411.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.4%</t>
+          <t>-609.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.7%</t>
+          <t>-280.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-59.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.4%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-347.7%</t>
+          <t>-344.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-167.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-308.6%</t>
+          <t>-305.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-209.0%</t>
+          <t>-207.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-180.7%</t>
         </is>
       </c>
     </row>
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2061111240075822</v>
+        <v>-0.1773899318021211</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.05203420450278</v>
+        <v>3.063522681384964</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.469932633914661</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.016794658768356</v>
+        <v>4.034027374091633</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2718785140569943</v>
+        <v>-0.2431573218515332</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.026744857613485</v>
+        <v>3.038233334495669</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.469932633914661</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.017812267898827</v>
+        <v>4.035044983222103</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2854139978337039</v>
+        <v>-0.2566928056282428</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.011958696090557</v>
+        <v>3.023447172972741</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.469932633914661</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.008440299886582</v>
+        <v>4.025673015209859</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3671858982614556</v>
+        <v>-0.3384647060559944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.969332661874694</v>
+        <v>2.980821138756879</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.496968207320798</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.014744369885502</v>
+        <v>4.031977085208779</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4343950061333333</v>
+        <v>-0.4056738139278721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.947214335559645</v>
+        <v>2.95870281244183</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.496968207320798</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.019509686719204</v>
+        <v>4.036742402042481</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6419607905249451</v>
+        <v>-0.613239598319484</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.862012817922241</v>
+        <v>2.873501294804425</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.289402422929186</v>
+        <v>1.318123615134647</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.892795012203478</v>
+        <v>3.910027727526755</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.059714814071782</v>
+        <v>-1.030993621866321</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.692838100008569</v>
+        <v>2.704326576890754</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8716483993823488</v>
+        <v>0.9003695915878102</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.640069489580439</v>
+        <v>3.657302204903716</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.2813367476299</v>
+        <v>-1.252615555424438</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.604055543184244</v>
+        <v>2.615544020066428</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8341222656949798</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.617420025966939</v>
+        <v>3.634652741290216</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.489340805982977</v>
+        <v>-1.460619613777516</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.525746064396938</v>
+        <v>2.537234541279123</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8341222656949798</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.622312170520865</v>
+        <v>3.639544885844141</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.700753226870952</v>
+        <v>-1.672032034665491</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.436262552379736</v>
+        <v>2.447751029261921</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6227098448070048</v>
+        <v>0.6514310370124661</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.490546174326068</v>
+        <v>3.507778889649344</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.039911604459475</v>
+        <v>-2.011190412254013</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.293683500650777</v>
+        <v>2.305171977532961</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2835514672184827</v>
+        <v>0.312272659423944</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.280135447079403</v>
+        <v>3.29736816240268</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.367928826186954</v>
+        <v>-2.339207633981492</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.182814901698553</v>
+        <v>2.194303378580738</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.04446575450899648</v>
+        <v>-0.01574456230353516</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.103663403781684</v>
+        <v>3.120896119104961</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.861253697722132</v>
+        <v>-2.83253250551667</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.993583703493051</v>
+        <v>2.005072180375235</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1494518687486152</v>
+        <v>-0.1207306765431539</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.048770485646481</v>
+        <v>3.066003200969758</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.353638725746229</v>
+        <v>-3.324917533540767</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.797736084327144</v>
+        <v>1.809224561209329</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6418368967727119</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.754445860875756</v>
+        <v>2.771678576199033</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.738819116676301</v>
+        <v>-3.71009792447084</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.642206466767978</v>
+        <v>1.653694943650163</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6418368967727119</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.752988399688619</v>
+        <v>2.770221115011896</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.082501889902963</v>
+        <v>-4.053780697697502</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.506502480931929</v>
+        <v>1.517990957814114</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7497429487999301</v>
+        <v>-0.7210217565944688</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.690013891926904</v>
+        <v>2.707246607250181</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.440152240141312</v>
+        <v>-4.41143104793585</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.359548399492848</v>
+        <v>1.371036876375032</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.107393299038278</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.471529740440153</v>
+        <v>2.48876245576343</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.749386343137362</v>
+        <v>-4.720665150931901</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.237627684994687</v>
+        <v>1.249116161876872</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.107393299038278</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.473302667140413</v>
+        <v>2.49053538246369</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.18119213628715</v>
+        <v>-5.152470944081688</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.051238255202177</v>
+        <v>1.062726732084361</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.243810795479545</v>
+        <v>-1.215089603274084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.377785056743057</v>
+        <v>2.395017772066334</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.415886130419702</v>
+        <v>-5.387164938214241</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9456454325512462</v>
+        <v>0.957133909433431</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.23747452825029</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.369871592082701</v>
+        <v>2.387104307405978</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.751548777650155</v>
+        <v>-5.722827585444693</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8099609653150304</v>
+        <v>0.8214494421972152</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.23747452825029</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.368452183738666</v>
+        <v>2.385684899061943</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.115175022550468</v>
+        <v>-6.086453830345007</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6709980275891465</v>
+        <v>0.6824865044713313</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.335696165117416</v>
+        <v>-1.306974972911954</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.316006761852632</v>
+        <v>2.333239477175909</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.480302405189215</v>
+        <v>-6.451581212983753</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5242015895394796</v>
+        <v>0.5356900664216639</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.632006949416428</v>
+        <v>-1.603285757210967</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.137474806279056</v>
+        <v>2.154707521602333</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.888891182369893</v>
+        <v>-6.860169990164431</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3595276226819673</v>
+        <v>0.3710160995641516</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.891083083985408</v>
+        <v>1.908315799308685</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.301873666510986</v>
+        <v>-7.273152474305525</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1895200614969905</v>
+        <v>0.2010085383791749</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.886268516456869</v>
+        <v>1.903501231780145</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.718265540797984</v>
+        <v>-7.689544348592523</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.02095736239106882</v>
+        <v>0.03244583927325317</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.884262567065746</v>
+        <v>1.901495282389023</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.094942551327827</v>
+        <v>-8.066221359122366</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1194547511521895</v>
+        <v>-0.1079662742700052</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.894521257734425</v>
+        <v>1.911753973057702</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.440817373312637</v>
+        <v>-8.412096181107175</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2617051148004181</v>
+        <v>-0.2502166379182338</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.89062082288012</v>
+        <v>1.907853538203397</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.60295964377573</v>
+        <v>-8.574238451570269</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3281571029306547</v>
+        <v>-0.3166686260484699</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.040595726597107</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.889025742935121</v>
+        <v>1.906258458258398</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.899620985585928</v>
+        <v>-8.870899793380467</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4430426637255258</v>
+        <v>-0.431554186843341</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.109338862330985</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.851558837424002</v>
+        <v>1.868791552747279</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.332970093696163</v>
+        <v>-9.304248901490702</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6204086115040228</v>
+        <v>-0.6089201346218385</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.109338862330985</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.847532532889599</v>
+        <v>1.864765248212876</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.715971482438794</v>
+        <v>-9.687250290233333</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7737112683226592</v>
+        <v>-0.7622227914404749</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.109338862330985</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.847430431568015</v>
+        <v>1.864663146891292</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.873370362651915</v>
+        <v>-9.844649170446454</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8340993044364775</v>
+        <v>-0.8226108275542932</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.266737742544106</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.755562619411573</v>
+        <v>1.772795334734849</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.23290068515592</v>
+        <v>-10.20417949295046</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9725611301400283</v>
+        <v>-0.9610726532578431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.266737742544106</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.760912922709623</v>
+        <v>1.778145638032899</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.55930071382093</v>
+        <v>-10.53057952161547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.095205121648856</v>
+        <v>-1.083716644766672</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.593137771209119</v>
+        <v>-2.564416579003658</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.572988925467792</v>
+        <v>1.590221640791069</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.77844968189513</v>
+        <v>-10.74972848968967</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.179822958256766</v>
+        <v>-1.168334481374581</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.812286739283317</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.444541295245043</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.77475875693872</v>
+        <v>-10.74603756473326</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.178346588274202</v>
+        <v>-1.166858111392017</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.812286739283317</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.444541295245043</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.97901693226858</v>
+        <v>-10.95029574006312</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.254536661287505</v>
+        <v>-1.24304818440532</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.939925683897306</v>
+        <v>-2.911204491691844</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.373471125595292</v>
+        <v>1.390703840918569</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.19705470389976</v>
+        <v>-11.1683335116943</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.337269215455539</v>
+        <v>-1.325780738573355</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.114696451993205</v>
+        <v>-3.085975259787743</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.273091219222188</v>
+        <v>1.290323934545465</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.12358487223231</v>
+        <v>-11.09486368002685</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.292509581295139</v>
+        <v>-1.281021104412955</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.041226620325756</v>
+        <v>-3.012505428120295</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.332544819716079</v>
+        <v>1.349777535039355</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.29870928961885</v>
+        <v>-11.26998809741339</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.348004127502239</v>
+        <v>-1.336515650620055</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.2163510377123</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.242025390031669</v>
+        <v>1.259258105354946</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.53316138363334</v>
+        <v>-11.50444019142788</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.449004130009631</v>
+        <v>-1.437515653127447</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.2163510377123</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.234806225130073</v>
+        <v>1.25203894045335</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.82096522817058</v>
+        <v>-11.79224403596512</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.570797858598503</v>
+        <v>-1.559309381716318</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.504154882249538</v>
+        <v>-3.475433690044077</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.055451727633754</v>
+        <v>1.072684442957031</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.05078967533441</v>
+        <v>-12.02206848312894</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.661611847625477</v>
+        <v>-1.650123370743292</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.666802419319699</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9589789952302139</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.28281859507067</v>
+        <v>-12.25409740286521</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.751729686890866</v>
+        <v>-1.740241210008682</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.728815116508122</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9244651055462749</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.23080308110185</v>
+        <v>-12.20208188889639</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.726933145616941</v>
+        <v>-1.715444668734756</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.728815116508122</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9284554412326758</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.37247492282597</v>
+        <v>-12.34375373062051</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.78507710920533</v>
+        <v>-1.773588632323146</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.728815116508122</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9269802143339341</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.47138166328525</v>
+        <v>-12.44266047107979</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.809586395224169</v>
+        <v>-1.798097918341984</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.827721856967397</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8826895802232411</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.27222955604815</v>
+        <v>-12.24350836384269</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.742976685976012</v>
+        <v>-1.731488209093828</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.662399331017584</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9688319621464458</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.04638440332874</v>
+        <v>-12.01766321112328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.643059551852039</v>
+        <v>-1.631571074969854</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.620472655430421</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.003567040534953</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.76010959100605</v>
+        <v>-11.73138839880058</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.527410482366902</v>
+        <v>-1.515922005484717</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.620472655430421</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.004706185091012</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.81300487905033</v>
+        <v>-11.78428368684487</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.545934823422509</v>
+        <v>-1.534446346540324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.615517309341974</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.010313166906187</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.52909614812158</v>
+        <v>-11.50037495591612</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.426637626812373</v>
+        <v>-1.415149149930188</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.615517309341974</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.016046871144824</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.41367522398349</v>
+        <v>-11.38495403177802</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.390206519551</v>
+        <v>-1.378718042668814</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.500096385203879</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.075562163233815</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14983835677942</v>
+        <v>-11.12111716457395</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.294555253982279</v>
+        <v>-1.283066777100094</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.500096385203879</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.065678681920908</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.88259655591102</v>
+        <v>-10.85387536370556</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.189493094134294</v>
+        <v>-1.178004617252109</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.500096385203879</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.063844121421534</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.7592906274328</v>
+        <v>-10.73056943522734</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.140471037716468</v>
+        <v>-1.128982560834282</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.410678714076316</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.117194409124611</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.73533708645684</v>
+        <v>-10.70661589425138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.130221115180591</v>
+        <v>-1.118732638298405</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.386725173100358</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.132235039855679</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.47127714813405</v>
+        <v>-10.44255595592858</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.037857456013224</v>
+        <v>-1.026368979131039</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.122665234777562</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.277410686687605</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.764197524629209</v>
+        <v>-9.735476332423746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7578126402715899</v>
+        <v>-0.7463241633894047</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.122665234777562</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.274623653027304</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.724013226263018</v>
+        <v>-9.695292034057555</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7413952970372724</v>
+        <v>-0.7299068201550871</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.082480936411371</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.29907785593486</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.643943430725214</v>
+        <v>-9.615222238519751</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7100005576013935</v>
+        <v>-0.6985120807192082</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.002411140873567</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.346486554478299</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.410462208495616</v>
+        <v>-9.381741016290153</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6086836398717024</v>
+        <v>-0.5971951629895171</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.768929918643968</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.494499716653911</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.230753678351743</v>
+        <v>-9.20203248614628</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.539692438127112</v>
+        <v>-0.5282039612449267</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.711758414481273</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.525910408838569</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.098478204720855</v>
+        <v>-9.069757012515392</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.49141476192773</v>
+        <v>-0.4799262850455448</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.579482940850386</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.600643179764128</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.907878530047702</v>
+        <v>-8.879157337842239</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4123598313708321</v>
+        <v>-0.4008713544886469</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.388883266177233</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.717818045255656</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.658878731364121</v>
+        <v>-8.630157539158658</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2998535706737409</v>
+        <v>-0.2883650937915556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.388883266177233</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.730724386479315</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.764468721137225</v>
+        <v>-8.735747528931762</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4700654961822011</v>
+        <v>-0.4585770193000158</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.494473255950338</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.539394463016234</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457897</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.783203623255822</v>
+        <v>-8.754482431050359</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4290151151525539</v>
+        <v>-0.4175266382703686</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.494473255950338</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.58793880489332</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.635263581848223</v>
+        <v>-8.60654238964276</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4897180212776817</v>
+        <v>-0.4782295443954965</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.47415234004178</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.480252431750287</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.611034945459251</v>
+        <v>-8.582313753253787</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4887405529755706</v>
+        <v>-0.4772520760933854</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.449923703652808</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.486075627330192</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.567486538688559</v>
+        <v>-8.538765346483096</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4782818023623872</v>
+        <v>-0.4667933254802019</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.449923703652808</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.479115015235099</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.325338145234701</v>
+        <v>-8.296616953029238</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3669600905997008</v>
+        <v>-0.3554716137175156</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.449923703652808</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.493577369616242</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.262108773466354</v>
+        <v>-8.233387581260891</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3471362214331668</v>
+        <v>-0.3356477445509816</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.449923703652808</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.488109490075437</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.138817638649224</v>
+        <v>-8.110096446443761</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3003216734957381</v>
+        <v>-0.2888331966135529</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.326632568835678</v>
+        <v>-2.297911376630216</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.559582264976292</v>
+        <v>1.576814980299569</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.117668439745781</v>
+        <v>-8.088947247540318</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2841610156970358</v>
+        <v>-0.2726725388148505</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.305483369932234</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.579972762555684</v>
+        <v>1.59720547787896</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.873902997762337</v>
+        <v>-7.845181805556874</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1908741305566077</v>
+        <v>-0.1793856536744225</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.305483369932234</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.575753470902734</v>
+        <v>1.592986186226011</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.609874930569077</v>
+        <v>-7.581153738363614</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08313858975928756</v>
+        <v>-0.07165011287710232</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.103617971116281</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.698997024112322</v>
+        <v>1.716229739435599</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.360024536620003</v>
+        <v>-7.33130334441454</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.009543642804044072</v>
+        <v>0.02103211968622931</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.103617971116281</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.691739099096024</v>
+        <v>1.708971814419301</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.056457047616024</v>
+        <v>-7.027735855410561</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1345697619262847</v>
+        <v>0.1460582388084699</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.103617971116281</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.695338222616673</v>
+        <v>1.71257093793995</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.98297713876401</v>
+        <v>-6.954255946558547</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1772892315216437</v>
+        <v>0.1887777084038289</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.030138062264267</v>
+        <v>-2.001416870058805</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.752753673982435</v>
+        <v>1.769986389305712</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.757944139095187</v>
+        <v>-6.729222946889724</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2663229090054697</v>
+        <v>0.277811385887655</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.805105062595444</v>
+        <v>-1.776383870389982</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.886793951400026</v>
+        <v>1.904026666723303</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.54330976145878</v>
+        <v>-6.514588569253317</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3568714611143498</v>
+        <v>0.368359937996535</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.590470684959037</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.020269379036188</v>
+        <v>2.037502094359464</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.276709404484428</v>
+        <v>-6.247988212278965</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4447058626878864</v>
+        <v>0.4561943395700716</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.590470684959037</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.001463637819983</v>
+        <v>2.01869635314326</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.036278907679568</v>
+        <v>-6.007557715474105</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5426211380347077</v>
+        <v>0.5541096149168929</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.350040188154177</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.147465012527777</v>
+        <v>2.164697727851054</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.793488100030123</v>
+        <v>-5.76476690782466</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6436667749293061</v>
+        <v>0.6551552518114914</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.350040188154177</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.151394326362597</v>
+        <v>2.168627041685874</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.677548250404937</v>
+        <v>-5.648827058199474</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6907212986967202</v>
+        <v>0.7022097755789054</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.273218457138053</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.198165948889611</v>
+        <v>2.215398664212888</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.434892661981774</v>
+        <v>-5.406171469776311</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7847816052859793</v>
+        <v>0.7962700821681645</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.273218457138053</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.195164020109605</v>
+        <v>2.212396735432882</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.214871863944763</v>
+        <v>-5.1861506717393</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8743689615113976</v>
+        <v>0.8858574383935829</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.131998612070072</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.281474964161007</v>
+        <v>2.298707679484284</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.015623234039954</v>
+        <v>-4.986902041834491</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9699625962751446</v>
+        <v>0.9814510731573298</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.131998612070072</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.29736914696283</v>
+        <v>2.314601862286107</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.856108130520584</v>
+        <v>-4.827386938315121</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.034914482123194</v>
+        <v>1.04640295900538</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9724835085507025</v>
+        <v>-0.9437623163452412</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.394224053514754</v>
+        <v>2.411456768838031</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.711435985420847</v>
+        <v>-4.682714793215384</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.102871442724529</v>
+        <v>1.114359919606714</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.8278113634509652</v>
+        <v>-0.7990901712455039</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.491115443136037</v>
+        <v>2.508348158459313</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.771310812778539</v>
+        <v>-4.742589620573076</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.064959003182878</v>
+        <v>1.076447480065063</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.8876861908086573</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.441228038122847</v>
+        <v>2.458460753446124</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.047708851382481</v>
+        <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.684511314999531</v>
+        <v>-4.737034060164913</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.173547901068922</v>
+        <v>1.101070197550895</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.8876861908086573</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.515097136897287</v>
+        <v>2.48086124676869</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.047781252755894</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.584818700270519</v>
+        <v>-4.637341445435901</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.213497348333939</v>
+        <v>1.141019644815912</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7879935760796455</v>
+        <v>-0.7592723838741842</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.574985107108107</v>
+        <v>2.540749216979509</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.058788175230596</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.653188886594529</v>
+        <v>-4.705711631759911</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.197156196279037</v>
+        <v>1.12467849276101</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7787178770434305</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.591557449004537</v>
+        <v>2.55732155887594</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.049224883862487</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.531772456968053</v>
+        <v>-4.584295202133434</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.236159476761518</v>
+        <v>1.163681773243492</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7787178770434305</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.581994157636429</v>
+        <v>2.547758267507831</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.873934448902874</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.562765616296758</v>
+        <v>-4.61528836146214</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.048471778070423</v>
+        <v>0.9759940745523963</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7787178770434305</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.406703722676816</v>
+        <v>2.372467832548218</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.878501680894662</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.387291356504289</v>
+        <v>-4.43981410166967</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.123228713979199</v>
+        <v>1.050751010461172</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7787178770434305</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.411270954668603</v>
+        <v>2.377035064540006</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.878513154781459</v>
+        <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.498227609145538</v>
+        <v>-4.550750354310919</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.078865686809497</v>
+        <v>1.00638798329147</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7787178770434305</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.411282428555401</v>
+        <v>2.377046538426804</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.881644540001365</v>
+        <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.701254186688771</v>
+        <v>-4.753776931854152</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.000786441012109</v>
+        <v>0.9283087374940822</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9817444545866639</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.292597867249366</v>
+        <v>2.258361977120769</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.891816926433497</v>
+        <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.543328587753478</v>
+        <v>-4.595851332918859</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.074129067018359</v>
+        <v>1.001651363500332</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9817444545866639</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.302770253681499</v>
+        <v>2.268534363552901</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.886763197007357</v>
+        <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.691649841564606</v>
+        <v>-4.744172586729988</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.009746836067767</v>
+        <v>0.9372691325497406</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9817444545866639</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.297716524255359</v>
+        <v>2.263480634126762</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.878538972451883</v>
+        <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.692832926215667</v>
+        <v>-4.745355671381049</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.001049377651869</v>
+        <v>0.9285716741338419</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9873875030531755</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.286106470619978</v>
+        <v>2.251870580491381</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.879090845484984</v>
+        <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.569705219221584</v>
+        <v>-4.622227964386965</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.050852333482604</v>
+        <v>0.9783746299645766</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9873875030531755</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.286658343653079</v>
+        <v>2.252422453524482</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.80836353737635</v>
+        <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.476894737770724</v>
+        <v>-4.529417482936106</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.017249217954313</v>
+        <v>0.9447715144362863</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8945770216023161</v>
+        <v>-0.8658558293968548</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.271617324414961</v>
+        <v>2.237381434286363</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.810237013300951</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.428331685549694</v>
+        <v>-4.480854430715076</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.038547914767326</v>
+        <v>0.9660702112492989</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8460139693812859</v>
+        <v>-0.8172927771758246</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.30262863167218</v>
+        <v>2.268392741543582</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.742979813506719</v>
+        <v>3.540891831353195</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.763588057015547</v>
+        <v>2.659982819434036</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.428331685549694</v>
+        <v>-4.480854430715076</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.038547914767326</v>
+        <v>0.9660702112492989</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.8460139693812859</v>
+        <v>-0.8172927771758246</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.756651854001915</v>
+        <v>2.653046616420404</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>135.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>411.2%</t>
+          <t>413.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.7%</t>
+          <t>-587.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.6%</t>
+          <t>-270.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-168.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.7%</t>
+          <t>-300.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-158.8%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-11.88119921246111</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.593775662476157</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.590281323900257</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>1.004891652481879</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.11322813219737</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.683893501741548</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.65229402108868</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.97037776279794</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.06121261822856</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.659096960467622</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.65229402108868</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9743680984843408</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.20288445995268</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.717240924056012</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.65229402108868</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.9728928715855991</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.30179120041195</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.741750210074849</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.751200761547956</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.9286022374749061</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.10263909317485</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.675140500826692</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.585878235598142</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.014744619398111</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-11.87679394045544</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.57522336670272</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.543951560010979</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.049479697786618</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.59051912813275</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.459574297217582</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.543951560010979</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.050618842342677</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.64341441617703</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.47809863827319</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.538996213922533</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.056225824157852</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.35950568524829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.358801441663053</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.538996213922533</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.061959528396489</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.24408476111019</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.322370334401681</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.423575289784437</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.121474820485481</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-10.98024789390612</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.22671906883296</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.423575289784437</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.111591339172573</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.71300609303772</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.121656908984975</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.423575289784437</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.109756778673199</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.5897001645595</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.072634852567148</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.334157618656874</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.163107066376276</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.56574662358354</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.062384930031271</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.310204077680917</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.178147697107344</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.30168668526075</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-0.9700212708639047</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.04614413935812</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.32332334393927</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.59460706175591</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.6899764551222707</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.04614413935812</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.320536310278969</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.55442276338972</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.6735591118879531</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-3.005959840991929</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.344990513186525</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.474352967851916</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.6421643724520743</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.925890045454125</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.392399211729964</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.240871745622318</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.5408474547223827</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.692408823224527</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.540412373905576</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.061163215478444</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.4718562529777928</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.635237319061831</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.571823066090234</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-8.928887741847557</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.4235785767784108</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.502961845430944</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.646555837015793</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.738288067174404</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.3445236462215124</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.312362170757792</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.763730702507321</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.489288268490823</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.2320173855244216</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.312362170757792</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.77663704373098</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.594878258263927</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.4022293110328818</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.417952160530896</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.585307120267899</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.613613160382524</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.3611789300032342</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.417952160530896</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.633851462144985</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.465673118974925</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.4218818361283621</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.397631244622338</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.526165089001952</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879205</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.441444482585952</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.4209043678262514</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.373402608233366</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.531988284581857</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.397896075815261</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.4104456172130679</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.373402608233366</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.525027672486764</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.296616953029238</v>
+        <v>-8.155747682361403</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3554716137175156</v>
+        <v>-0.2991239054503816</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.373402608233366</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.539490026867907</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.233387581260891</v>
+        <v>-8.092518310593055</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3356477445509816</v>
+        <v>-0.2793000362838476</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.373402608233366</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.534022147327102</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262048</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.110096446443761</v>
+        <v>-7.969227175775925</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2888331966135529</v>
+        <v>-0.2324854883464185</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.250111473416236</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.605494922227958</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.088947247540318</v>
+        <v>-7.948077976872481</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2726725388148505</v>
+        <v>-0.2163248305477161</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.228962274512793</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.625885419807349</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.845181805556874</v>
+        <v>-7.704312534889037</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1793856536744225</v>
+        <v>-0.1230379454072876</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.228962274512793</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.621666128154399</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.581153738363614</v>
+        <v>-7.440284467695777</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07165011287710232</v>
+        <v>-0.0153024046099679</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.027096875696839</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.716229739435599</v>
+        <v>1.744909681363987</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.33130334441454</v>
+        <v>-7.190434073746703</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02103211968622931</v>
+        <v>0.07737982795336418</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.027096875696839</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.708971814419301</v>
+        <v>1.737651756347689</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.027735855410561</v>
+        <v>-6.886866584742724</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1460582388084699</v>
+        <v>0.2024059470756043</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.027096875696839</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.71257093793995</v>
+        <v>1.741250879868338</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.954255946558547</v>
+        <v>-6.81338667589071</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1887777084038289</v>
+        <v>0.2451254166709638</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.001416870058805</v>
+        <v>-1.953616966844825</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.769986389305712</v>
+        <v>1.7986663312341</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.729222946889724</v>
+        <v>-6.588353676221887</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.277811385887655</v>
+        <v>0.3341590941547898</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.776383870389982</v>
+        <v>-1.728583967176002</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.904026666723303</v>
+        <v>1.932706608651691</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.514588569253317</v>
+        <v>-6.37371929858548</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.368359937996535</v>
+        <v>0.4247076462636699</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.513949589539595</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.037502094359464</v>
+        <v>2.066182036287853</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.247988212278965</v>
+        <v>-6.107118941611128</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4561943395700716</v>
+        <v>0.5125420478372065</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.513949589539595</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.01869635314326</v>
+        <v>2.047376295071648</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.007557715474105</v>
+        <v>-5.866688444806268</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5541096149168929</v>
+        <v>0.6104573231840278</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.273519092734735</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.164697727851054</v>
+        <v>2.193377669779442</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.76476690782466</v>
+        <v>-5.623897637156823</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6551552518114914</v>
+        <v>0.7115029600786262</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.273519092734735</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.168627041685874</v>
+        <v>2.197306983614262</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.648827058199474</v>
+        <v>-5.507957787531637</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7022097755789054</v>
+        <v>0.7585574838460403</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.196697361718611</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.215398664212888</v>
+        <v>2.244078606141276</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406171469776311</v>
+        <v>-5.265302199108474</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7962700821681645</v>
+        <v>0.8526177904352994</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.196697361718611</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.212396735432882</v>
+        <v>2.24107667736127</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.1861506717393</v>
+        <v>-5.045281401071463</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8858574383935829</v>
+        <v>0.9422051466607178</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.055477516650631</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.298707679484284</v>
+        <v>2.327387621412672</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.986902041834491</v>
+        <v>-4.846032771166654</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9814510731573298</v>
+        <v>1.037798781424465</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.055477516650631</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.314601862286107</v>
+        <v>2.343281804214495</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.827386938315121</v>
+        <v>-4.686517667647284</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.04640295900538</v>
+        <v>1.102750667272514</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9437623163452412</v>
+        <v>-0.8959624131312608</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.411456768838031</v>
+        <v>2.440136710766419</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.682714793215384</v>
+        <v>-4.541845522547547</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.114359919606714</v>
+        <v>1.170707627873849</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7990901712455039</v>
+        <v>-0.7512902680315234</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.508348158459313</v>
+        <v>2.537028100387702</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.742589620573076</v>
+        <v>-4.601720349905239</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.076447480065063</v>
+        <v>1.132795188332198</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8111650953892156</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.458460753446124</v>
+        <v>2.487140695374512</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.737034060164913</v>
+        <v>-4.514920852126231</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.101070197550895</v>
+        <v>1.189915480766368</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8111650953892156</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.48086124676869</v>
+        <v>2.509541188697078</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.637341445435901</v>
+        <v>-4.415228237397219</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.141019644815912</v>
+        <v>1.229864928031384</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7592723838741842</v>
+        <v>-0.7114724806602037</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.540749216979509</v>
+        <v>2.569429158907897</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.705711631759911</v>
+        <v>-4.483598423721229</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.12467849276101</v>
+        <v>1.213523775976482</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7021967816239888</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.55732155887594</v>
+        <v>2.586001500804328</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.584295202133434</v>
+        <v>-4.362181994094753</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.163681773243492</v>
+        <v>1.252527056458964</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7021967816239888</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.547758267507831</v>
+        <v>2.576438209436219</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.61528836146214</v>
+        <v>-4.393175153423458</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9759940745523963</v>
+        <v>1.064839357767869</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7021967816239888</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.372467832548218</v>
+        <v>2.401147774476606</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.43981410166967</v>
+        <v>-4.217700893630989</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.050751010461172</v>
+        <v>1.139596293676645</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7021967816239888</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.377035064540006</v>
+        <v>2.405715006468394</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.550750354310919</v>
+        <v>-4.328637146272238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.00638798329147</v>
+        <v>1.095233266506943</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7021967816239888</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.377046538426804</v>
+        <v>2.405726480355192</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.753776931854152</v>
+        <v>-4.531663723815471</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9283087374940822</v>
+        <v>1.017154020709555</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9052233591672222</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.258361977120769</v>
+        <v>2.287041919049157</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.595851332918859</v>
+        <v>-4.373738124880178</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.001651363500332</v>
+        <v>1.090496646715804</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9052233591672222</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.268534363552901</v>
+        <v>2.297214305481289</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.744172586729988</v>
+        <v>-4.522059378691306</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9372691325497406</v>
+        <v>1.026114415765213</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9052233591672222</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.263480634126762</v>
+        <v>2.29216057605515</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.745355671381049</v>
+        <v>-4.523242463342367</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9285716741338419</v>
+        <v>1.017416957349315</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.9108664076337337</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.251870580491381</v>
+        <v>2.280550522419769</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.622227964386965</v>
+        <v>-4.400114756348284</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9783746299645766</v>
+        <v>1.067219913180049</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.9108664076337337</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.252422453524482</v>
+        <v>2.28110239545287</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.529417482936106</v>
+        <v>-4.307304274897424</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9447715144362863</v>
+        <v>1.033616797651759</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8658558293968548</v>
+        <v>-0.8180559261828744</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.237381434286363</v>
+        <v>2.266061376214751</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.480854430715076</v>
+        <v>-4.258741222676394</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9660702112492989</v>
+        <v>1.054915494464772</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8172927771758246</v>
+        <v>-0.7694928739618442</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.268392741543582</v>
+        <v>2.297072683471971</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.540891831353195</v>
+        <v>3.8165693290485</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.659982819434036</v>
+        <v>2.879186910092419</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.480854430715076</v>
+        <v>-4.258741222676394</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9660702112492989</v>
+        <v>1.054915494464772</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.8172927771758246</v>
+        <v>-0.7694928739618442</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.653046616420404</v>
+        <v>2.872250707078787</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-51.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.9%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-721.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>413.7%</t>
+          <t>441.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.4%</t>
+          <t>-599.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-289.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.7%</t>
+          <t>-291.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.8%</t>
+          <t>-168.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-300.9%</t>
+          <t>-291.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-158.8%</t>
+          <t>-226.2%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.4685151026334585</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>2.938718254170654</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.5502870030612101</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>2.896092219954792</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.6174961109330879</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>2.873973893639743</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.8250618953246998</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.788772376002339</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-1.242815918871537</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.619597658088667</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.464437852429654</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.530815101264342</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.672441910782731</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.452505622477037</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.883854331670706</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.363022110459835</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-2.223012709259229</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.220443058730875</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.551029930986708</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.109574459778651</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-3.044354802521886</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>1.920343261573149</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.536739830545983</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.724495642407242</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.921920221476055</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.568966024848077</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-4.265602994702718</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.433262039012028</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.623253344941066</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.286307957572946</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.932487447937117</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.164387243074785</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.364293241086904</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>0.9779978132822751</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.598987235219457</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>0.8724049906313445</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.934649882449909</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.7367205233951286</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-6.298276127350222</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.5977575856692448</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.663403509988969</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.4509611476195778</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-7.071992287169648</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.2862871807620651</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.484974771310742</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.1162796195770883</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.901366645597739</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>-0.05228307952883338</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-8.278043656127583</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.1926951930720917</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.623918478112392</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.3349455567203203</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.786060748575485</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.4013975448505565</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-9.082722090385683</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.5162831056454276</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.516071198495919</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.693649053423925</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.89907258723855</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.8469517102425614</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-10.05647146745167</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.9073397463563793</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.41600178995567</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-1.04580157205993</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.74240181862069</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.168445563568758</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.96155078669488</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.253063400176668</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.95785986173847</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.251587030194103</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-11.16211803706834</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.327777103207406</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.38015580869951</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.410509657375442</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-11.30668597703206</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.365750023215041</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.48181039441861</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.421244569422141</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.7162624884331</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.522244571929533</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-12.00406633297034</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.644038300518405</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.88119921246111</v>
+        <v>-12.09302150946632</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.593775662476157</v>
+        <v>-1.678504581278244</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.590281323900257</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.11322813219737</v>
+        <v>-12.32505042920259</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.683893501741548</v>
+        <v>-1.768622420543634</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.65229402108868</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.06121261822856</v>
+        <v>-12.27303491523377</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.659096960467622</v>
+        <v>-1.743825879269708</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.65229402108868</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.20288445995268</v>
+        <v>-12.41470675695789</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.717240924056012</v>
+        <v>-1.801969842858098</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.65229402108868</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.30179120041195</v>
+        <v>-12.51361349741717</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.741750210074849</v>
+        <v>-1.826479128876936</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.751200761547956</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.10263909317485</v>
+        <v>-12.31446139018007</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.675140500826692</v>
+        <v>-1.759869419628779</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.585878235598142</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.87679394045544</v>
+        <v>-12.08861623746066</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.57522336670272</v>
+        <v>-1.659952285504807</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.543951560010979</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.59051912813275</v>
+        <v>-11.80234142513796</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.459574297217582</v>
+        <v>-1.544303216019669</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.543951560010979</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.64341441617703</v>
+        <v>-11.85523671318225</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.47809863827319</v>
+        <v>-1.562827557075276</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.538996213922533</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.35950568524829</v>
+        <v>-11.5713279822535</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.358801441663053</v>
+        <v>-1.44353036046514</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.538996213922533</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.24408476111019</v>
+        <v>-11.45590705811541</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.322370334401681</v>
+        <v>-1.407099253203767</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.423575289784437</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.98024789390612</v>
+        <v>-11.19207019091134</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.22671906883296</v>
+        <v>-1.311447987635046</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.423575289784437</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.71300609303772</v>
+        <v>-10.92482839004294</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.121656908984975</v>
+        <v>-1.206385827787062</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.423575289784437</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.5897001645595</v>
+        <v>-10.80152246156472</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.072634852567148</v>
+        <v>-1.157363771369235</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.334157618656874</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.56574662358354</v>
+        <v>-10.77756892058876</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.062384930031271</v>
+        <v>-1.147113848833358</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.310204077680917</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.30168668526075</v>
+        <v>-10.51350898226596</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9700212708639047</v>
+        <v>-1.054750189665992</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.04614413935812</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.59460706175591</v>
+        <v>-9.806429358761127</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6899764551222707</v>
+        <v>-0.7747053739243572</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.04614413935812</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.55442276338972</v>
+        <v>-9.766245060394937</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6735591118879531</v>
+        <v>-0.7582880306900397</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.005959840991929</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.474352967851916</v>
+        <v>-9.686175264857132</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6421643724520743</v>
+        <v>-0.7268932912541608</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.925890045454125</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.240871745622318</v>
+        <v>-9.452694042627535</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5408474547223827</v>
+        <v>-0.6255763735244697</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.692408823224527</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.061163215478444</v>
+        <v>-9.272985512483661</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4718562529777928</v>
+        <v>-0.5565851717798793</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.635237319061831</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.928887741847557</v>
+        <v>-9.140710038852774</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4235785767784108</v>
+        <v>-0.5083074955804974</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.502961845430944</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.738288067174404</v>
+        <v>-8.95011036417962</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3445236462215124</v>
+        <v>-0.4292525650235994</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.312362170757792</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.489288268490823</v>
+        <v>-8.819033859275777</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2320173855244216</v>
+        <v>-0.363915621838403</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.312362170757792</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.594878258263927</v>
+        <v>-8.924623849048881</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4022293110328818</v>
+        <v>-0.5341275473468636</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.417952160530896</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457897</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.613613160382524</v>
+        <v>-8.943358751167478</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3611789300032342</v>
+        <v>-0.493077166317216</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.417952160530896</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.465673118974925</v>
+        <v>-8.795418709759879</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4218818361283621</v>
+        <v>-0.5537800724423438</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.397631244622338</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.441444482585952</v>
+        <v>-8.771190073370907</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4209043678262514</v>
+        <v>-0.5528026041402332</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.373402608233366</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.397896075815261</v>
+        <v>-8.727641666600215</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4104456172130679</v>
+        <v>-0.5423438535270497</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.373402608233366</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.155747682361403</v>
+        <v>-8.485493273146357</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2991239054503816</v>
+        <v>-0.4310221417643634</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.373402608233366</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.092518310593055</v>
+        <v>-8.42226390137801</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2793000362838476</v>
+        <v>-0.4111982725978294</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.373402608233366</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.969227175775925</v>
+        <v>-8.29897276656088</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2324854883464185</v>
+        <v>-0.3643837246604007</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.250111473416236</v>
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.948077976872481</v>
+        <v>-8.182757038937767</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2163248305477161</v>
+        <v>-0.3101964553738306</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.228962274512793</v>
+        <v>-2.133895745793123</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.625885419807349</v>
+        <v>1.682925337039151</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.704312534889037</v>
+        <v>-7.938991596954323</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1230379454072876</v>
+        <v>-0.2169095702334021</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.228962274512793</v>
+        <v>-2.133895745793123</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.621666128154399</v>
+        <v>1.678706045386201</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.440284467695777</v>
+        <v>-7.674963529761063</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0153024046099679</v>
+        <v>-0.1091740294360823</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.027096875696839</v>
+        <v>-1.932030346977169</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.744909681363987</v>
+        <v>1.801949598595789</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.190434073746703</v>
+        <v>-7.425113135811989</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.07737982795336418</v>
+        <v>-0.01649179687275026</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.027096875696839</v>
+        <v>-1.932030346977169</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.737651756347689</v>
+        <v>1.794691673579492</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.886866584742724</v>
+        <v>-7.12154564680801</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2024059470756043</v>
+        <v>0.1085343222494899</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.027096875696839</v>
+        <v>-1.932030346977169</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.741250879868338</v>
+        <v>1.79829079710014</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.81338667589071</v>
+        <v>-7.048065737955996</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2451254166709638</v>
+        <v>0.1512537918448493</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.953616966844825</v>
+        <v>-1.858550438125155</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.7986663312341</v>
+        <v>1.855706248465903</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.588353676221887</v>
+        <v>-6.823032738287173</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3341590941547898</v>
+        <v>0.2402874693286754</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.728583967176002</v>
+        <v>-1.633517438456332</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.932706608651691</v>
+        <v>1.989746525883493</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.37371929858548</v>
+        <v>-6.608398360650766</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4247076462636699</v>
+        <v>0.3308360214375554</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.513949589539595</v>
+        <v>-1.418883060819925</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.066182036287853</v>
+        <v>2.123221953519654</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.107118941611128</v>
+        <v>-6.341798003676415</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5125420478372065</v>
+        <v>0.418670423011092</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.513949589539595</v>
+        <v>-1.418883060819925</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.047376295071648</v>
+        <v>2.10441621230345</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.866688444806268</v>
+        <v>-6.101367506871554</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6104573231840278</v>
+        <v>0.5165856983579133</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.273519092734735</v>
+        <v>-1.178452564015065</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.193377669779442</v>
+        <v>2.250417587011244</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.623897637156823</v>
+        <v>-5.858576699222109</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7115029600786262</v>
+        <v>0.6176313352525118</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.273519092734735</v>
+        <v>-1.178452564015065</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.197306983614262</v>
+        <v>2.254346900846064</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.507957787531637</v>
+        <v>-5.742636849596924</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7585574838460403</v>
+        <v>0.6646858590199258</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.196697361718611</v>
+        <v>-1.101630832998941</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.244078606141276</v>
+        <v>2.301118523373078</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.265302199108474</v>
+        <v>-5.49998126117376</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8526177904352994</v>
+        <v>0.758746165609185</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.196697361718611</v>
+        <v>-1.101630832998941</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.24107667736127</v>
+        <v>2.298116594593072</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.045281401071463</v>
+        <v>-5.279960463136749</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9422051466607178</v>
+        <v>0.8483335218346033</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.055477516650631</v>
+        <v>-0.9604109879309608</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.327387621412672</v>
+        <v>2.384427538644474</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.846032771166654</v>
+        <v>-5.08071183323194</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.037798781424465</v>
+        <v>0.9439271565983502</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.055477516650631</v>
+        <v>-0.9604109879309608</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.343281804214495</v>
+        <v>2.400321721446297</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.686517667647284</v>
+        <v>-4.92119672971257</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.102750667272514</v>
+        <v>1.0088790424464</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8959624131312608</v>
+        <v>-0.8008958844115909</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.440136710766419</v>
+        <v>2.497176627998221</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.541845522547547</v>
+        <v>-4.776524584612833</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.170707627873849</v>
+        <v>1.076836003047735</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7512902680315234</v>
+        <v>-0.6562237393118535</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.537028100387702</v>
+        <v>2.594068017619503</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.601720349905239</v>
+        <v>-4.836399411970525</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.132795188332198</v>
+        <v>1.038923563506084</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.8111650953892156</v>
+        <v>-0.7160985666695456</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.487140695374512</v>
+        <v>2.544180612606314</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.514920852126231</v>
+        <v>-4.749599914191517</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.189915480766368</v>
+        <v>1.096043855940253</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.8111650953892156</v>
+        <v>-0.7160985666695456</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.509541188697078</v>
+        <v>2.56658110592888</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.415228237397219</v>
+        <v>-4.649907299462505</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.229864928031384</v>
+        <v>1.13599330320527</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7114724806602037</v>
+        <v>-0.6164059519405338</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.569429158907897</v>
+        <v>2.626469076139699</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.483598423721229</v>
+        <v>-4.718277485786516</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.213523775976482</v>
+        <v>1.119652151150368</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7021967816239888</v>
+        <v>-0.6071302529043189</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.586001500804328</v>
+        <v>2.64304141803613</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.362181994094753</v>
+        <v>-4.596861056160039</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.252527056458964</v>
+        <v>1.15865543163285</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7021967816239888</v>
+        <v>-0.6071302529043189</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.576438209436219</v>
+        <v>2.633478126668022</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.393175153423458</v>
+        <v>-4.627854215488744</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.064839357767869</v>
+        <v>0.9709677329417545</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7021967816239888</v>
+        <v>-0.6071302529043189</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.401147774476606</v>
+        <v>2.458187691708408</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.217700893630989</v>
+        <v>-4.452379955696275</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.139596293676645</v>
+        <v>1.04572466885053</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7021967816239888</v>
+        <v>-0.6071302529043189</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.405715006468394</v>
+        <v>2.462754923700196</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.328637146272238</v>
+        <v>-4.563316208337524</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.095233266506943</v>
+        <v>1.001361641680828</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7021967816239888</v>
+        <v>-0.6071302529043189</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.405726480355192</v>
+        <v>2.462766397586994</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.531663723815471</v>
+        <v>-4.766342785880757</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.017154020709555</v>
+        <v>0.9232823958834404</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9052233591672222</v>
+        <v>-0.8101568304475523</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.287041919049157</v>
+        <v>2.344081836280959</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.373738124880178</v>
+        <v>-4.608417186945464</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.090496646715804</v>
+        <v>0.9966250218896899</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9052233591672222</v>
+        <v>-0.8101568304475523</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.297214305481289</v>
+        <v>2.354254222713092</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.522059378691306</v>
+        <v>-4.756738440756592</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.026114415765213</v>
+        <v>0.9322427909390987</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9052233591672222</v>
+        <v>-0.8101568304475523</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.29216057605515</v>
+        <v>2.349200493286952</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.523242463342367</v>
+        <v>-4.757921525407653</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.017416957349315</v>
+        <v>0.9235453325232001</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9108664076337337</v>
+        <v>-0.8157998789140638</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.280550522419769</v>
+        <v>2.337590439651571</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.400114756348284</v>
+        <v>-4.63479381841357</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.067219913180049</v>
+        <v>0.9733482883539348</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9108664076337337</v>
+        <v>-0.8157998789140638</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.28110239545287</v>
+        <v>2.338142312684672</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.307304274897424</v>
+        <v>-4.54198333696271</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.033616797651759</v>
+        <v>0.9397451728256443</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8180559261828744</v>
+        <v>-0.7229893974632045</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.266061376214751</v>
+        <v>2.323101293446554</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.258741222676394</v>
+        <v>-4.49342028474168</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.054915494464772</v>
+        <v>0.9610438696386572</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7694928739618442</v>
+        <v>-0.6744263452421743</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.297072683471971</v>
+        <v>2.354112600703772</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.8165693290485</v>
+        <v>3.400130007456826</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.879186910092419</v>
+        <v>2.602407521172796</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.258741222676394</v>
+        <v>-4.379796518577194</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.054915494464772</v>
+        <v>0.8501324894281705</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7694928739618442</v>
+        <v>-0.6744263452421743</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.872250707078787</v>
+        <v>2.197751714027491</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240428.xlsx
+++ b/tame_output/ON/bt/strategyON_20240428.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-36.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-721.5%</t>
+          <t>-720.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-58.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.3%</t>
+          <t>440.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.6%</t>
+          <t>-610.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-289.0%</t>
+          <t>-288.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-112.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-291.2%</t>
+          <t>-280.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-167.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.4%</t>
+          <t>-294.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-226.2%</t>
+          <t>-212.8%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4685151026334585</v>
+        <v>-0.4601661445192873</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.938718254170654</v>
+        <v>2.942057837416323</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5502870030612101</v>
+        <v>-0.541938044947039</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.896092219954792</v>
+        <v>2.899431803200461</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6174961109330879</v>
+        <v>-0.6091471528189167</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.873973893639743</v>
+        <v>2.877313476885412</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8250618953246998</v>
+        <v>-0.8167129372105286</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.788772376002339</v>
+        <v>2.792111959248007</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.242815918871537</v>
+        <v>-1.234466960757366</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.619597658088667</v>
+        <v>2.622937241334336</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.464437852429654</v>
+        <v>-1.456088894315483</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.530815101264342</v>
+        <v>2.53415468451001</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.672441910782731</v>
+        <v>-1.66409295266856</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.452505622477037</v>
+        <v>2.455845205722705</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.883854331670706</v>
+        <v>-1.875505373556535</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.363022110459835</v>
+        <v>2.366361693705503</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.223012709259229</v>
+        <v>-2.214663751145058</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.220443058730875</v>
+        <v>2.223782641976543</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.551029930986708</v>
+        <v>-2.542680972872537</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.109574459778651</v>
+        <v>2.11291404302432</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.044354802521886</v>
+        <v>-3.036005844407715</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.920343261573149</v>
+        <v>1.923682844818817</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.536739830545983</v>
+        <v>-3.528390872431812</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.724495642407242</v>
+        <v>1.727835225652911</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.921920221476055</v>
+        <v>-3.913571263361884</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.568966024848077</v>
+        <v>1.572305608093745</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.265602994702718</v>
+        <v>-4.257254036588547</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.433262039012028</v>
+        <v>1.436601622257696</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.623253344941066</v>
+        <v>-4.614904386826895</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.286307957572946</v>
+        <v>1.289647540818615</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.932487447937117</v>
+        <v>-4.924138489822946</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.164387243074785</v>
+        <v>1.167726826320454</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.364293241086904</v>
+        <v>-5.355944282972733</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9779978132822751</v>
+        <v>0.9813373965279433</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.598987235219457</v>
+        <v>-5.590638277105286</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8724049906313445</v>
+        <v>0.8757445738770131</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.934649882449909</v>
+        <v>-5.926300924335738</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7367205233951286</v>
+        <v>0.7400601066407972</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.298276127350222</v>
+        <v>-6.289927169236051</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.5977575856692448</v>
+        <v>0.6010971689149134</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.663403509988969</v>
+        <v>-6.655054551874798</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4509611476195778</v>
+        <v>0.454300730865246</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.071992287169648</v>
+        <v>-7.063643329055477</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2862871807620651</v>
+        <v>0.2896267640077337</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.484974771310742</v>
+        <v>-7.476625813196571</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1162796195770883</v>
+        <v>0.1196192028227565</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.901366645597739</v>
+        <v>-7.893017687483568</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.05228307952883338</v>
+        <v>-0.04894349628316519</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.278043656127583</v>
+        <v>-8.269694698013412</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1926951930720917</v>
+        <v>-0.1893556098264235</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.623918478112392</v>
+        <v>-8.615569519998221</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3349455567203203</v>
+        <v>-0.3316059734746521</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.786060748575485</v>
+        <v>-8.777711790461314</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.4013975448505565</v>
+        <v>-0.3980579616048883</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.082722090385683</v>
+        <v>-9.074373132271512</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5162831056454276</v>
+        <v>-0.5129435223997594</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.516071198495919</v>
+        <v>-9.507722240381748</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.693649053423925</v>
+        <v>-0.6903094701782564</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.89907258723855</v>
+        <v>-9.890723629124379</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8469517102425614</v>
+        <v>-0.8436121269968933</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.05647146745167</v>
+        <v>-10.0481225093375</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9073397463563793</v>
+        <v>-0.9040001631107111</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.41600178995567</v>
+        <v>-10.4076528318415</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.04580157205993</v>
+        <v>-1.042461988814262</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.74240181862069</v>
+        <v>-10.73405286050651</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.168445563568758</v>
+        <v>-1.165105980323089</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.96155078669488</v>
+        <v>-10.95320182858071</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.253063400176668</v>
+        <v>-1.249723816930999</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.95785986173847</v>
+        <v>-10.9495109036243</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.251587030194103</v>
+        <v>-1.248247446948435</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.16211803706834</v>
+        <v>-11.15376907895416</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.327777103207406</v>
+        <v>-1.324437519961738</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.38015580869951</v>
+        <v>-11.37180685058534</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.410509657375442</v>
+        <v>-1.407170074129774</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.30668597703206</v>
+        <v>-11.29833701891789</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.365750023215041</v>
+        <v>-1.362410439969373</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.48181039441861</v>
+        <v>-11.47346143630444</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.421244569422141</v>
+        <v>-1.417904986176473</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.7162624884331</v>
+        <v>-11.70791353031893</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.522244571929533</v>
+        <v>-1.518904988683865</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.00406633297034</v>
+        <v>-11.99571737485616</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.644038300518405</v>
+        <v>-1.640698717272736</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.09302150946632</v>
+        <v>-12.22554182201999</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.678504581278244</v>
+        <v>-1.731512706299711</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.590281323900257</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.004891652481879</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.32505042920259</v>
+        <v>-12.45757074175625</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.768622420543634</v>
+        <v>-1.821630545565101</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.65229402108868</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.97037776279794</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.27303491523377</v>
+        <v>-12.40555522778744</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.743825879269708</v>
+        <v>-1.796834004291174</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.65229402108868</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9743680984843408</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.41470675695789</v>
+        <v>-12.54722706951156</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.801969842858098</v>
+        <v>-1.854977967879564</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.65229402108868</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9728928715855991</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.51361349741717</v>
+        <v>-12.64613380997083</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.826479128876936</v>
+        <v>-1.879487253898402</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.751200761547956</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9286022374749061</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.31446139018007</v>
+        <v>-12.44698170273374</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.759869419628779</v>
+        <v>-1.812877544650246</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.585878235598142</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.014744619398111</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08861623746066</v>
+        <v>-12.22113655001433</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.659952285504807</v>
+        <v>-1.712960410526273</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.543951560010979</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.049479697786618</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.80234142513796</v>
+        <v>-11.93486173769163</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.544303216019669</v>
+        <v>-1.597311341041136</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.543951560010979</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.050618842342677</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.85523671318225</v>
+        <v>-11.98775702573592</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.562827557075276</v>
+        <v>-1.615835682096743</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.538996213922533</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.056225824157852</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.5713279822535</v>
+        <v>-11.70384829480717</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.44353036046514</v>
+        <v>-1.496538485486607</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.538996213922533</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.061959528396489</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.45590705811541</v>
+        <v>-11.58842737066907</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.407099253203767</v>
+        <v>-1.460107378225233</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.423575289784437</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.121474820485481</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.19207019091134</v>
+        <v>-11.324590503465</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.311447987635046</v>
+        <v>-1.364456112656514</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.423575289784437</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.111591339172573</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.92482839004294</v>
+        <v>-11.0573487025966</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.206385827787062</v>
+        <v>-1.259393952808528</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.423575289784437</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.109756778673199</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.80152246156472</v>
+        <v>-10.93404277411839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.157363771369235</v>
+        <v>-1.210371896390701</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.334157618656874</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.163107066376276</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77756892058876</v>
+        <v>-10.91008923314243</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.147113848833358</v>
+        <v>-1.200121973854824</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.310204077680917</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.178147697107344</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.51350898226596</v>
+        <v>-10.64602929481963</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.054750189665992</v>
+        <v>-1.107758314687458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.04614413935812</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.32332334393927</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.806429358761127</v>
+        <v>-9.938949671314793</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7747053739243572</v>
+        <v>-0.8277134989458235</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.04614413935812</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.320536310278969</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.766245060394937</v>
+        <v>-9.898765372948603</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7582880306900397</v>
+        <v>-0.8112961557115059</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.005959840991929</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.344990513186525</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.686175264857132</v>
+        <v>-9.818695577410798</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7268932912541608</v>
+        <v>-0.7799014162756275</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.925890045454125</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.392399211729964</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.452694042627535</v>
+        <v>-9.585214355181201</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6255763735244697</v>
+        <v>-0.6785844985459359</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.692408823224527</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.540412373905576</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.272985512483661</v>
+        <v>-9.405505825037327</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5565851717798793</v>
+        <v>-0.6095932968013456</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.635237319061831</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.571823066090234</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.140710038852774</v>
+        <v>-9.27323035140644</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5083074955804974</v>
+        <v>-0.5613156206019636</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.502961845430944</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.646555837015793</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.95011036417962</v>
+        <v>-9.082630676733286</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4292525650235994</v>
+        <v>-0.4822606900450657</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.312362170757792</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.763730702507321</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.819033859275777</v>
+        <v>-8.833630878049705</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.363915621838403</v>
+        <v>-0.3697544293479744</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.312362170757792</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.77663704373098</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.924623849048881</v>
+        <v>-8.93922086782281</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5341275473468636</v>
+        <v>-0.5399663548564351</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.417952160530896</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.585307120267899</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.943358751167478</v>
+        <v>-8.957955769941407</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.493077166317216</v>
+        <v>-0.4989159738267874</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.417952160530896</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.633851462144985</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.795418709759879</v>
+        <v>-8.810015728533807</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5537800724423438</v>
+        <v>-0.5596188799519153</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.397631244622338</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.526165089001952</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.771190073370907</v>
+        <v>-8.785787092144835</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5528026041402332</v>
+        <v>-0.5586414116498046</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.373402608233366</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.531988284581857</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.727641666600215</v>
+        <v>-8.742238685374144</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5423438535270497</v>
+        <v>-0.5481826610366212</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.373402608233366</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.525027672486764</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.485493273146357</v>
+        <v>-8.500090291920285</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4310221417643634</v>
+        <v>-0.4368609492739348</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.373402608233366</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.539490026867907</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.42226390137801</v>
+        <v>-8.436860920151938</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4111982725978294</v>
+        <v>-0.4170370801074008</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.373402608233366</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.534022147327102</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.29897276656088</v>
+        <v>-8.313569785334808</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3643837246604007</v>
+        <v>-0.3702225321699717</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.250111473416236</v>
+        <v>-2.297911376630216</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.605494922227958</v>
+        <v>1.576814980299569</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.182757038937767</v>
+        <v>-8.292420586431366</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3101964553738306</v>
+        <v>-0.3540618743712698</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.133895745793123</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.682925337039151</v>
+        <v>1.59720547787896</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.938991596954323</v>
+        <v>-8.04865514444792</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2169095702334021</v>
+        <v>-0.2607749892308409</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.133895745793123</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.678706045386201</v>
+        <v>1.592986186226011</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.674963529761063</v>
+        <v>-7.78462707725466</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1091740294360823</v>
+        <v>-0.1530394484335207</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.932030346977169</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.801949598595789</v>
+        <v>1.716229739435599</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.425113135811989</v>
+        <v>-7.534776683305585</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01649179687275026</v>
+        <v>-0.06035721587018861</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.932030346977169</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.794691673579492</v>
+        <v>1.708971814419301</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.12154564680801</v>
+        <v>-7.231209194301607</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1085343222494899</v>
+        <v>0.06466890325205155</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.932030346977169</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.79829079710014</v>
+        <v>1.71257093793995</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.048065737955996</v>
+        <v>-7.157729285449593</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1512537918448493</v>
+        <v>0.1073883728474105</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.858550438125155</v>
+        <v>-2.001416870058805</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.855706248465903</v>
+        <v>1.769986389305712</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.823032738287173</v>
+        <v>-6.93269628578077</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2402874693286754</v>
+        <v>0.1964220503312371</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.633517438456332</v>
+        <v>-1.776383870389982</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.989746525883493</v>
+        <v>1.904026666723303</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.608398360650766</v>
+        <v>-6.718061908144363</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3308360214375554</v>
+        <v>0.2869706024401171</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.418883060819925</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.123221953519654</v>
+        <v>2.037502094359464</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.341798003676415</v>
+        <v>-6.451461551170011</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.418670423011092</v>
+        <v>0.3748050040136532</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.418883060819925</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.10441621230345</v>
+        <v>2.01869635314326</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.101367506871554</v>
+        <v>-6.211031054365151</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5165856983579133</v>
+        <v>0.4727202793604746</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.178452564015065</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.250417587011244</v>
+        <v>2.164697727851054</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.858576699222109</v>
+        <v>-5.968240246715705</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6176313352525118</v>
+        <v>0.573765916255073</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.178452564015065</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.254346900846064</v>
+        <v>2.168627041685874</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.742636849596924</v>
+        <v>-5.85230039709052</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6646858590199258</v>
+        <v>0.6208204400224875</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.101630832998941</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.301118523373078</v>
+        <v>2.215398664212888</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.49998126117376</v>
+        <v>-5.609644808667356</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.758746165609185</v>
+        <v>0.7148807466117462</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.101630832998941</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.298116594593072</v>
+        <v>2.212396735432882</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.279960463136749</v>
+        <v>-5.389624010630346</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8483335218346033</v>
+        <v>0.8044681028371645</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9604109879309608</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.384427538644474</v>
+        <v>2.298707679484284</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.08071183323194</v>
+        <v>-5.190375380725537</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9439271565983502</v>
+        <v>0.9000617376009115</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9604109879309608</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.400321721446297</v>
+        <v>2.314601862286107</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.92119672971257</v>
+        <v>-5.030860277206167</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.0088790424464</v>
+        <v>0.9650136234489612</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8008958844115909</v>
+        <v>-0.9437623163452412</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.497176627998221</v>
+        <v>2.411456768838031</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.776524584612833</v>
+        <v>-4.88618813210643</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.076836003047735</v>
+        <v>1.032970584050296</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6562237393118535</v>
+        <v>-0.7990901712455039</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.594068017619503</v>
+        <v>2.508348158459313</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.836399411970525</v>
+        <v>-4.946062959464122</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.038923563506084</v>
+        <v>0.995058144508645</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7160985666695456</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.544180612606314</v>
+        <v>2.458460753446124</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.749599914191517</v>
+        <v>-4.859263461685114</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.096043855940253</v>
+        <v>1.052178436942814</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7160985666695456</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.56658110592888</v>
+        <v>2.48086124676869</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.649907299462505</v>
+        <v>-4.759570846956102</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.13599330320527</v>
+        <v>1.092127884207831</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6164059519405338</v>
+        <v>-0.7592723838741842</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.626469076139699</v>
+        <v>2.540749216979509</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.718277485786516</v>
+        <v>-4.827941033280112</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.119652151150368</v>
+        <v>1.075786732152929</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6071302529043189</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.64304141803613</v>
+        <v>2.55732155887594</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.596861056160039</v>
+        <v>-4.706524603653635</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.15865543163285</v>
+        <v>1.114790012635411</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6071302529043189</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.633478126668022</v>
+        <v>2.547758267507831</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.627854215488744</v>
+        <v>-4.737517762982341</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9709677329417545</v>
+        <v>0.927102313944316</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6071302529043189</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.458187691708408</v>
+        <v>2.372467832548218</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.452379955696275</v>
+        <v>-4.562043503189871</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.04572466885053</v>
+        <v>1.001859249853092</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6071302529043189</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.462754923700196</v>
+        <v>2.377035064540006</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.563316208337524</v>
+        <v>-4.67297975583112</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.001361641680828</v>
+        <v>0.9574962226833894</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6071302529043189</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.462766397586994</v>
+        <v>2.377046538426804</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.766342785880757</v>
+        <v>-4.876006333374353</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9232823958834404</v>
+        <v>0.8794169768860018</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8101568304475523</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.344081836280959</v>
+        <v>2.258361977120769</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.608417186945464</v>
+        <v>-4.71808073443906</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9966250218896899</v>
+        <v>0.9527596028922514</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8101568304475523</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.354254222713092</v>
+        <v>2.268534363552901</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.756738440756592</v>
+        <v>-4.866401988250189</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9322427909390987</v>
+        <v>0.8883773719416601</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8101568304475523</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.349200493286952</v>
+        <v>2.263480634126762</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.757921525407653</v>
+        <v>-4.86758507290125</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9235453325232001</v>
+        <v>0.8796799135257616</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8157998789140638</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.337590439651571</v>
+        <v>2.251870580491381</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.63479381841357</v>
+        <v>-4.744457365907166</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9733482883539348</v>
+        <v>0.9294828693564963</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8157998789140638</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.338142312684672</v>
+        <v>2.252422453524482</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.54198333696271</v>
+        <v>-4.651646884456307</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9397451728256443</v>
+        <v>0.8958797538282057</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7229893974632045</v>
+        <v>-0.8658558293968548</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.323101293446554</v>
+        <v>2.237381434286363</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.49342028474168</v>
+        <v>-4.603083832235277</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9610438696386572</v>
+        <v>0.9171784506412186</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6744263452421743</v>
+        <v>-0.8172927771758246</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.354112600703772</v>
+        <v>2.268392741543582</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.400130007456826</v>
+        <v>3.400130007456827</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.602407521172796</v>
+        <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.379796518577194</v>
+        <v>-4.48822903813647</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8501324894281705</v>
+        <v>0.9581960767924642</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6744263452421743</v>
+        <v>-0.7024379830770178</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.197751714027491</v>
+        <v>2.332381326514589</v>
       </c>
     </row>
   </sheetData>
